--- a/data/trans_dic/P43B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43B-Estudios-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,93</t>
+          <t>3,85; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,1</t>
+          <t>2,84; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,2</t>
+          <t>3,35; 6,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,93</t>
+          <t>3,85; 6,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,1</t>
+          <t>2,84; 6,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,2</t>
+          <t>3,35; 6,88</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 22,35</t>
+          <t>15,05; 22,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,29</t>
+          <t>7,64; 11,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,62</t>
+          <t>13,76; 18,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 22,35</t>
+          <t>15,05; 22,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,29</t>
+          <t>7,64; 11,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,62</t>
+          <t>13,76; 18,02</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 53,66</t>
+          <t>36,12; 53,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 47,74</t>
+          <t>33,68; 46,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,54; 50,42</t>
+          <t>39,98; 49,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 53,66</t>
+          <t>36,12; 53,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 47,74</t>
+          <t>33,68; 46,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,54; 50,42</t>
+          <t>39,98; 49,25</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 16,26</t>
+          <t>12,65; 16,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 14,13</t>
+          <t>10,55; 13,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,56</t>
+          <t>16,75; 20,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 16,26</t>
+          <t>12,65; 16,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 14,13</t>
+          <t>10,55; 13,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,56</t>
+          <t>16,75; 20,17</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>20200</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30779; 57608</t>
+          <t>31988; 57022</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17049; 37062</t>
+          <t>17258; 37760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12932; 28626</t>
+          <t>14428; 29654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30779; 57608</t>
+          <t>31988; 57022</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17049; 37062</t>
+          <t>17258; 37760</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12932; 28626</t>
+          <t>14428; 29654</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>115173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>115173</t>
         </is>
       </c>
     </row>
@@ -1217,32 +1217,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101819; 143779</t>
+          <t>96810; 141822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65578; 102420</t>
+          <t>63678; 99792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52125; 142642</t>
+          <t>100676; 131870</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101819; 143779</t>
+          <t>96810; 141822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65578; 102420</t>
+          <t>63678; 99792</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52125; 142642</t>
+          <t>100676; 131870</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>133590</t>
         </is>
       </c>
     </row>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56878; 85041</t>
+          <t>57245; 84634</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82476; 115554</t>
+          <t>81518; 112255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108619; 135084</t>
+          <t>119584; 147325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56878; 85041</t>
+          <t>57245; 84634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82476; 115554</t>
+          <t>81518; 112255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>108619; 135084</t>
+          <t>119584; 147325</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>268963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>268963</t>
         </is>
       </c>
     </row>
@@ -1453,32 +1453,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>206545; 265551</t>
+          <t>206651; 264318</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179551; 237812</t>
+          <t>177688; 234490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>156220; 292978</t>
+          <t>244931; 294912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>206545; 265551</t>
+          <t>206651; 264318</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>179551; 237812</t>
+          <t>177688; 234490</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>156220; 292978</t>
+          <t>244931; 294912</t>
         </is>
       </c>
     </row>
